--- a/salidas/empresas/COF.xlsx
+++ b/salidas/empresas/COF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>60.365234375</v>
+        <v>60.36521530151367</v>
       </c>
       <c r="C2" t="n">
         <v>83.30000305175781</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>63.50226593017578</v>
+        <v>63.50231170654297</v>
       </c>
       <c r="C3" t="n">
         <v>87.59999847412109</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>58.36992645263672</v>
+        <v>58.36990737915039</v>
       </c>
       <c r="C4" t="n">
         <v>80.51999664306641</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>62.80637359619141</v>
+        <v>62.80640411376953</v>
       </c>
       <c r="C5" t="n">
         <v>86.63999938964844</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>61.96321487426758</v>
+        <v>61.96324157714844</v>
       </c>
       <c r="C7" t="n">
         <v>85.44999694824219</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>56.08957290649414</v>
+        <v>56.08958435058594</v>
       </c>
       <c r="C8" t="n">
         <v>77.34999847412109</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>53.02598571777344</v>
+        <v>53.02598190307617</v>
       </c>
       <c r="C9" t="n">
         <v>73.09999847412109</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>57.05918121337891</v>
+        <v>57.05916213989258</v>
       </c>
       <c r="C10" t="n">
         <v>78.66000366210938</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>57.5451774597168</v>
+        <v>57.54516983032227</v>
       </c>
       <c r="C11" t="n">
         <v>79.33000183105469</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>56.51303863525391</v>
+        <v>56.51301574707031</v>
       </c>
       <c r="C12" t="n">
         <v>77.87999725341797</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>55.74383544921875</v>
+        <v>55.74385070800781</v>
       </c>
       <c r="C13" t="n">
         <v>76.81999969482422</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>58.3416748046875</v>
+        <v>58.34164428710938</v>
       </c>
       <c r="C14" t="n">
         <v>80.40000152587891</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>55.91427993774414</v>
+        <v>55.9142951965332</v>
       </c>
       <c r="C15" t="n">
         <v>77.02999877929688</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>54.77466201782227</v>
+        <v>54.77465057373047</v>
       </c>
       <c r="C16" t="n">
         <v>75.45999908447266</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>53.90359497070312</v>
+        <v>53.90361785888672</v>
       </c>
       <c r="C17" t="n">
         <v>74.26000213623047</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>57.93121719360352</v>
+        <v>57.93122100830078</v>
       </c>
       <c r="C18" t="n">
         <v>79.77999877929688</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>56.95820236206055</v>
+        <v>56.95820617675781</v>
       </c>
       <c r="C19" t="n">
         <v>78.44000244140625</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>51.38144683837891</v>
+        <v>51.3814811706543</v>
       </c>
       <c r="C20" t="n">
         <v>70.76000213623047</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>46.96998977661133</v>
+        <v>46.96997451782227</v>
       </c>
       <c r="C21" t="n">
         <v>64.66000366210938</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>47.64553833007812</v>
+        <v>47.64554977416992</v>
       </c>
       <c r="C23" t="n">
         <v>65.58999633789062</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>38.74275970458984</v>
+        <v>38.74276733398438</v>
       </c>
       <c r="C24" t="n">
         <v>53.31000137329102</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>34.34594345092773</v>
+        <v>34.34595489501953</v>
       </c>
       <c r="C25" t="n">
         <v>47.2599983215332</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.69480895996094</v>
+        <v>39.69478607177734</v>
       </c>
       <c r="C26" t="n">
         <v>54.61999893188477</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>33.70711898803711</v>
+        <v>33.70712280273438</v>
       </c>
       <c r="C27" t="n">
         <v>46.02999877929688</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>36.0431022644043</v>
+        <v>36.04309463500977</v>
       </c>
       <c r="C28" t="n">
         <v>49.22000122070312</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>38.81116104125977</v>
+        <v>38.81112670898438</v>
       </c>
       <c r="C29" t="n">
         <v>53</v>
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>28.02810096740723</v>
+        <v>28.02809906005859</v>
       </c>
       <c r="C31" t="n">
         <v>38.0099983215332</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>30.86704635620117</v>
+        <v>30.86703300476074</v>
       </c>
       <c r="C32" t="n">
         <v>41.86000061035156</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.9227180480957</v>
+        <v>37.92272186279297</v>
       </c>
       <c r="C34" t="n">
         <v>51</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>29.08895111083984</v>
+        <v>29.08894157409668</v>
       </c>
       <c r="C35" t="n">
         <v>39.11999893188477</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>25.84015655517578</v>
+        <v>25.84014701843262</v>
       </c>
       <c r="C36" t="n">
         <v>34.40999984741211</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.94775390625</v>
+        <v>23.94775772094727</v>
       </c>
       <c r="C37" t="n">
         <v>31.88999938964844</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.294206619262695</v>
+        <v>9.294203758239746</v>
       </c>
       <c r="C39" t="n">
         <v>12.05000019073486</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.440757751464844</v>
+        <v>9.440751075744629</v>
       </c>
       <c r="C40" t="n">
         <v>12.23999977111816</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.91161727905273</v>
+        <v>12.91161823272705</v>
       </c>
       <c r="C41" t="n">
         <v>16.73999977111816</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>18.89284896850586</v>
+        <v>18.89285087585449</v>
       </c>
       <c r="C42" t="n">
         <v>24.44000053405762</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>16.91389274597168</v>
+        <v>16.91388320922852</v>
       </c>
       <c r="C43" t="n">
         <v>21.8799991607666</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.87115478515625</v>
+        <v>28.87116050720215</v>
       </c>
       <c r="C45" t="n">
         <v>37.29000091552734</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>27.66335487365723</v>
+        <v>27.6633415222168</v>
       </c>
       <c r="C46" t="n">
         <v>35.72999954223633</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>28.33693313598633</v>
+        <v>28.33692741394043</v>
       </c>
       <c r="C47" t="n">
         <v>36.59999847412109</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>29.73823547363281</v>
+        <v>29.73824691772461</v>
       </c>
       <c r="C48" t="n">
         <v>38.36000061035156</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>29.72274208068848</v>
+        <v>29.72274398803711</v>
       </c>
       <c r="C49" t="n">
         <v>38.34000015258789</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.57538032531738</v>
+        <v>28.57538604736328</v>
       </c>
       <c r="C50" t="n">
         <v>36.86000061035156</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>29.30681228637695</v>
+        <v>29.30683326721191</v>
       </c>
       <c r="C51" t="n">
         <v>37.75</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.14823532104492</v>
+        <v>32.14820861816406</v>
       </c>
       <c r="C52" t="n">
         <v>41.40999984741211</v>
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.10005187988281</v>
+        <v>32.10005950927734</v>
       </c>
       <c r="C54" t="n">
         <v>41.29999923706055</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.32280349731445</v>
+        <v>31.32279777526855</v>
       </c>
       <c r="C55" t="n">
         <v>40.29999923706055</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.90060806274414</v>
+        <v>32.90061569213867</v>
       </c>
       <c r="C56" t="n">
         <v>42.33000183105469</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>29.4701099395752</v>
+        <v>29.47012138366699</v>
       </c>
       <c r="C57" t="n">
         <v>37.86999893188477</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.77748680114746</v>
+        <v>30.77747535705566</v>
       </c>
       <c r="C58" t="n">
         <v>39.54999923706055</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>29.00321388244629</v>
+        <v>29.00320625305176</v>
       </c>
       <c r="C59" t="n">
         <v>37.27000045776367</v>
@@ -1674,7 +1686,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>37.52451705932617</v>
+        <v>37.52455139160156</v>
       </c>
       <c r="C62" t="n">
         <v>48.15999984741211</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>38.81661605834961</v>
+        <v>38.81661224365234</v>
       </c>
       <c r="C63" t="n">
         <v>49.77000045776367</v>
@@ -1774,11 +1786,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>40.52463912963867</v>
+        <v>40.52464294433594</v>
       </c>
       <c r="C64" t="n">
         <v>51.95999908447266</v>
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>42.68500518798828</v>
+        <v>42.68501281738281</v>
       </c>
       <c r="C65" t="n">
         <v>54.72999954223633</v>
@@ -1832,11 +1844,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>42.41913986206055</v>
+        <v>42.41915512084961</v>
       </c>
       <c r="C66" t="n">
         <v>54.34000015258789</v>
@@ -1861,11 +1873,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>40.33488464355469</v>
+        <v>40.33488082885742</v>
       </c>
       <c r="C67" t="n">
         <v>51.66999816894531</v>
@@ -1890,11 +1902,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>37.31386184692383</v>
+        <v>37.31385803222656</v>
       </c>
       <c r="C68" t="n">
         <v>47.79999923706055</v>
@@ -1919,11 +1931,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>35.99186325073242</v>
+        <v>35.99185943603516</v>
       </c>
       <c r="C69" t="n">
         <v>46.04999923706055</v>
@@ -1948,11 +1960,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>30.97411155700684</v>
+        <v>30.9741039276123</v>
       </c>
       <c r="C70" t="n">
         <v>39.63000106811523</v>
@@ -1977,7 +1989,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2006,11 +2018,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>34.94699478149414</v>
+        <v>34.94698715209961</v>
       </c>
       <c r="C72" t="n">
         <v>44.65999984741211</v>
@@ -2035,11 +2047,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>33.09245681762695</v>
+        <v>33.09245300292969</v>
       </c>
       <c r="C73" t="n">
         <v>42.29000091552734</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>35.7999153137207</v>
+        <v>35.7999267578125</v>
       </c>
       <c r="C74" t="n">
         <v>45.75</v>
@@ -2093,11 +2105,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>39.63702774047852</v>
+        <v>39.63701629638672</v>
       </c>
       <c r="C75" t="n">
         <v>50.59999847412109</v>
@@ -2122,11 +2134,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>43.66339492797852</v>
+        <v>43.66339111328125</v>
       </c>
       <c r="C76" t="n">
         <v>55.7400016784668</v>
@@ -2151,11 +2163,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>43.45972442626953</v>
+        <v>43.4597282409668</v>
       </c>
       <c r="C77" t="n">
         <v>55.47999954223633</v>
@@ -2180,11 +2192,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>40.27946853637695</v>
+        <v>40.27947235107422</v>
       </c>
       <c r="C78" t="n">
         <v>51.36999893188477</v>
@@ -2209,11 +2221,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>42.85916519165039</v>
+        <v>42.85916900634766</v>
       </c>
       <c r="C79" t="n">
         <v>54.65999984741211</v>
@@ -2238,11 +2250,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>44.29409027099609</v>
+        <v>44.29409408569336</v>
       </c>
       <c r="C80" t="n">
         <v>56.4900016784668</v>
@@ -2267,11 +2279,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.36465072631836</v>
+        <v>44.36464691162109</v>
       </c>
       <c r="C81" t="n">
         <v>56.52999877929688</v>
@@ -2296,11 +2308,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>44.7413444519043</v>
+        <v>44.74134063720703</v>
       </c>
       <c r="C82" t="n">
         <v>57.0099983215332</v>
@@ -2325,11 +2337,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>47.22130966186523</v>
+        <v>47.2213134765625</v>
       </c>
       <c r="C83" t="n">
         <v>60.16999816894531</v>
@@ -2354,11 +2366,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.24142837524414</v>
+        <v>45.2414436340332</v>
       </c>
       <c r="C84" t="n">
         <v>57.59999847412109</v>
@@ -2383,7 +2395,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2412,11 +2424,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>44.2360725402832</v>
+        <v>44.23605728149414</v>
       </c>
       <c r="C86" t="n">
         <v>56.31999969482422</v>
@@ -2441,11 +2453,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>40.1159782409668</v>
+        <v>40.11597442626953</v>
       </c>
       <c r="C87" t="n">
         <v>51.02999877929688</v>
@@ -2470,11 +2482,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.19759368896484</v>
+        <v>43.19759750366211</v>
       </c>
       <c r="C88" t="n">
         <v>54.95000076293945</v>
@@ -2499,11 +2511,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>45.42232513427734</v>
+        <v>45.42231750488281</v>
       </c>
       <c r="C89" t="n">
         <v>57.77999877929688</v>
@@ -2528,11 +2540,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>48.13996887207031</v>
+        <v>48.13995742797852</v>
       </c>
       <c r="C90" t="n">
         <v>60.93000030517578</v>
@@ -2557,11 +2569,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>49.62533187866211</v>
+        <v>49.62532806396484</v>
       </c>
       <c r="C91" t="n">
         <v>62.81000137329102</v>
@@ -2586,11 +2598,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>54.53176879882812</v>
+        <v>54.53176498413086</v>
       </c>
       <c r="C92" t="n">
         <v>69.01999664306641</v>
@@ -2615,11 +2627,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>51.22272491455078</v>
+        <v>51.22272109985352</v>
       </c>
       <c r="C93" t="n">
         <v>64.55000305175781</v>
@@ -2644,11 +2656,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>54.54764175415039</v>
+        <v>54.54762268066406</v>
       </c>
       <c r="C94" t="n">
         <v>68.73999786376953</v>
@@ -2673,11 +2685,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>54.4920654296875</v>
+        <v>54.4920768737793</v>
       </c>
       <c r="C95" t="n">
         <v>68.66999816894531</v>
@@ -2702,11 +2714,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>57.08574295043945</v>
+        <v>57.08573532104492</v>
       </c>
       <c r="C96" t="n">
         <v>71.62999725341797</v>
@@ -2731,11 +2743,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>61.05456924438477</v>
+        <v>61.05458831787109</v>
       </c>
       <c r="C97" t="n">
         <v>76.61000061035156</v>
@@ -2760,11 +2772,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>56.27285003662109</v>
+        <v>56.27284240722656</v>
       </c>
       <c r="C98" t="n">
         <v>70.61000061035156</v>
@@ -2789,11 +2801,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>58.777099609375</v>
+        <v>58.77705383300781</v>
       </c>
       <c r="C99" t="n">
         <v>73.43000030517578</v>
@@ -2818,11 +2830,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>61.76274871826172</v>
+        <v>61.76276397705078</v>
       </c>
       <c r="C100" t="n">
         <v>77.16000366210938</v>
@@ -2847,11 +2859,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>59.15328216552734</v>
+        <v>59.15329360961914</v>
       </c>
       <c r="C101" t="n">
         <v>73.90000152587891</v>
@@ -2876,11 +2888,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>63.39641571044922</v>
+        <v>63.39640808105469</v>
       </c>
       <c r="C102" t="n">
         <v>78.88999938964844</v>
@@ -2905,7 +2917,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2934,11 +2946,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>63.91875076293945</v>
+        <v>63.91875457763672</v>
       </c>
       <c r="C104" t="n">
         <v>79.54000091552734</v>
@@ -2963,11 +2975,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>66.19597625732422</v>
+        <v>66.19595336914062</v>
       </c>
       <c r="C105" t="n">
         <v>82.05999755859375</v>
@@ -2992,11 +3004,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>65.84105682373047</v>
+        <v>65.84103393554688</v>
       </c>
       <c r="C106" t="n">
         <v>81.62000274658203</v>
@@ -3021,11 +3033,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>66.76875305175781</v>
+        <v>66.76871490478516</v>
       </c>
       <c r="C107" t="n">
         <v>82.76999664306641</v>
@@ -3050,11 +3062,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>67.36324310302734</v>
+        <v>67.36322784423828</v>
       </c>
       <c r="C108" t="n">
         <v>83.19999694824219</v>
@@ -3079,11 +3091,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>66.83695220947266</v>
+        <v>66.83697509765625</v>
       </c>
       <c r="C109" t="n">
         <v>82.55000305175781</v>
@@ -3108,11 +3120,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>59.27477264404297</v>
+        <v>59.27480697631836</v>
       </c>
       <c r="C110" t="n">
         <v>73.20999908447266</v>
@@ -3137,11 +3149,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>63.98281860351562</v>
+        <v>63.98282623291016</v>
       </c>
       <c r="C111" t="n">
         <v>78.70999908447266</v>
@@ -3166,7 +3178,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3195,11 +3207,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>65.722412109375</v>
+        <v>65.72238159179688</v>
       </c>
       <c r="C113" t="n">
         <v>80.84999847412109</v>
@@ -3224,11 +3236,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>68.25572967529297</v>
+        <v>68.25571441650391</v>
       </c>
       <c r="C114" t="n">
         <v>83.55999755859375</v>
@@ -3253,11 +3265,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>71.85801696777344</v>
+        <v>71.85800933837891</v>
       </c>
       <c r="C115" t="n">
         <v>87.97000122070312</v>
@@ -3282,11 +3294,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>66.40965270996094</v>
+        <v>66.40964508056641</v>
       </c>
       <c r="C116" t="n">
         <v>81.30000305175781</v>
@@ -3311,11 +3323,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>63.82169342041016</v>
+        <v>63.82167434692383</v>
       </c>
       <c r="C117" t="n">
         <v>77.75</v>
@@ -3340,7 +3352,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3369,7 +3381,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3398,11 +3410,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>64.76718902587891</v>
+        <v>64.76719665527344</v>
       </c>
       <c r="C120" t="n">
         <v>78.51000213623047</v>
@@ -3427,7 +3439,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3456,11 +3468,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>54.13351821899414</v>
+        <v>54.13350677490234</v>
       </c>
       <c r="C122" t="n">
         <v>65.62000274658203</v>
@@ -3485,11 +3497,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>54.57500457763672</v>
+        <v>54.57499313354492</v>
       </c>
       <c r="C123" t="n">
         <v>65.73000335693359</v>
@@ -3514,11 +3526,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>57.54742813110352</v>
+        <v>57.54742431640625</v>
       </c>
       <c r="C124" t="n">
         <v>69.30999755859375</v>
@@ -3543,11 +3555,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>60.104736328125</v>
+        <v>60.10474014282227</v>
       </c>
       <c r="C125" t="n">
         <v>72.38999938964844</v>
@@ -3572,11 +3584,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>61.15823745727539</v>
+        <v>61.15821838378906</v>
       </c>
       <c r="C126" t="n">
         <v>73.23999786376953</v>
@@ -3601,11 +3613,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>53.03328704833984</v>
+        <v>53.03327941894531</v>
       </c>
       <c r="C127" t="n">
         <v>63.5099983215332</v>
@@ -3630,11 +3642,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>56.01437759399414</v>
+        <v>56.01436996459961</v>
       </c>
       <c r="C128" t="n">
         <v>67.08000183105469</v>
@@ -3659,11 +3671,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>60.1502685546875</v>
+        <v>60.15028762817383</v>
       </c>
       <c r="C129" t="n">
         <v>71.59999847412109</v>
@@ -3688,11 +3700,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>60.34352493286133</v>
+        <v>60.34353256225586</v>
       </c>
       <c r="C130" t="n">
         <v>71.83000183105469</v>
@@ -3717,11 +3729,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>62.20009994506836</v>
+        <v>62.20009613037109</v>
       </c>
       <c r="C131" t="n">
         <v>74.04000091552734</v>
@@ -3746,11 +3758,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>70.9908447265625</v>
+        <v>70.99082183837891</v>
       </c>
       <c r="C132" t="n">
         <v>84.04000091552734</v>
@@ -3775,11 +3787,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>73.69396209716797</v>
+        <v>73.6939697265625</v>
       </c>
       <c r="C133" t="n">
         <v>87.23999786376953</v>
@@ -3804,11 +3816,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>73.82065582275391</v>
+        <v>73.82067108154297</v>
       </c>
       <c r="C134" t="n">
         <v>87.38999938964844</v>
@@ -3833,11 +3845,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>79.64998626708984</v>
+        <v>79.64997863769531</v>
       </c>
       <c r="C135" t="n">
         <v>93.86000061035156</v>
@@ -3862,7 +3874,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3891,11 +3903,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>68.21079254150391</v>
+        <v>68.21078491210938</v>
       </c>
       <c r="C137" t="n">
         <v>80.37999725341797</v>
@@ -3920,11 +3932,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>65.59590911865234</v>
+        <v>65.59589385986328</v>
       </c>
       <c r="C138" t="n">
         <v>76.91999816894531</v>
@@ -3949,11 +3961,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>70.45677947998047</v>
+        <v>70.45677185058594</v>
       </c>
       <c r="C139" t="n">
         <v>82.62000274658203</v>
@@ -3978,7 +3990,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4007,11 +4019,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>68.20821380615234</v>
+        <v>68.20820617675781</v>
       </c>
       <c r="C141" t="n">
         <v>79.61000061035156</v>
@@ -4036,11 +4048,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>72.53496551513672</v>
+        <v>72.53497314453125</v>
       </c>
       <c r="C142" t="n">
         <v>84.66000366210938</v>
@@ -4065,11 +4077,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>78.97794342041016</v>
+        <v>78.97793579101562</v>
       </c>
       <c r="C143" t="n">
         <v>92.18000030517578</v>
@@ -4094,11 +4106,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>79.18318176269531</v>
+        <v>79.18317413330078</v>
       </c>
       <c r="C144" t="n">
         <v>92</v>
@@ -4123,11 +4135,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>85.70720672607422</v>
+        <v>85.70718383789062</v>
       </c>
       <c r="C145" t="n">
         <v>99.58000183105469</v>
@@ -4152,11 +4164,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>89.47697448730469</v>
+        <v>89.47701263427734</v>
       </c>
       <c r="C146" t="n">
         <v>103.9599990844727</v>
@@ -4181,11 +4193,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>84.65592193603516</v>
+        <v>84.65589904785156</v>
       </c>
       <c r="C147" t="n">
         <v>97.93000030517578</v>
@@ -4210,11 +4222,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>82.83193206787109</v>
+        <v>82.83191680908203</v>
       </c>
       <c r="C148" t="n">
         <v>95.81999969482422</v>
@@ -4239,11 +4251,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>78.33676910400391</v>
+        <v>78.33675384521484</v>
       </c>
       <c r="C149" t="n">
         <v>90.62000274658203</v>
@@ -4268,11 +4280,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>81.61088562011719</v>
+        <v>81.61087036132812</v>
       </c>
       <c r="C150" t="n">
         <v>94</v>
@@ -4297,7 +4309,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4326,11 +4338,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>81.88869476318359</v>
+        <v>81.88870239257812</v>
       </c>
       <c r="C152" t="n">
         <v>94.31999969482422</v>
@@ -4355,11 +4367,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>86.39086151123047</v>
+        <v>86.390869140625</v>
       </c>
       <c r="C153" t="n">
         <v>99.08999633789062</v>
@@ -4384,11 +4396,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>82.76399993896484</v>
+        <v>82.76400756835938</v>
       </c>
       <c r="C154" t="n">
         <v>94.93000030517578</v>
@@ -4413,11 +4425,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>77.85552215576172</v>
+        <v>77.85550689697266</v>
       </c>
       <c r="C155" t="n">
         <v>89.30000305175781</v>
@@ -4442,11 +4454,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>78.53378295898438</v>
+        <v>78.53376007080078</v>
       </c>
       <c r="C156" t="n">
         <v>89.68000030517578</v>
@@ -4471,7 +4483,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4500,11 +4512,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>70.57355499267578</v>
+        <v>70.57357788085938</v>
       </c>
       <c r="C158" t="n">
         <v>80.58999633789062</v>
@@ -4529,7 +4541,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4558,11 +4570,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>71.90077209472656</v>
+        <v>71.90074920654297</v>
       </c>
       <c r="C160" t="n">
         <v>81.69000244140625</v>
@@ -4587,11 +4599,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>81.70582580566406</v>
+        <v>81.70581817626953</v>
       </c>
       <c r="C161" t="n">
         <v>92.83000183105469</v>
@@ -4616,11 +4628,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>75.91652679443359</v>
+        <v>75.91651916503906</v>
       </c>
       <c r="C162" t="n">
         <v>85.87000274658203</v>
@@ -4645,11 +4657,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>80.22203063964844</v>
+        <v>80.22202301025391</v>
       </c>
       <c r="C163" t="n">
         <v>90.73999786376953</v>
@@ -4674,11 +4686,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>81.70729064941406</v>
+        <v>81.707275390625</v>
       </c>
       <c r="C164" t="n">
         <v>92.41999816894531</v>
@@ -4703,7 +4715,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4732,11 +4744,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>80.78815460205078</v>
+        <v>80.78814697265625</v>
       </c>
       <c r="C166" t="n">
         <v>90.98000335693359</v>
@@ -4761,11 +4773,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>82.80384063720703</v>
+        <v>82.80386352539062</v>
       </c>
       <c r="C167" t="n">
         <v>93.25</v>
@@ -4790,11 +4802,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>89.17166137695312</v>
+        <v>89.17167663574219</v>
       </c>
       <c r="C168" t="n">
         <v>100.0100021362305</v>
@@ -4819,11 +4831,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>91.75740051269531</v>
+        <v>91.75737762451172</v>
       </c>
       <c r="C169" t="n">
         <v>102.9100036621094</v>
@@ -4848,11 +4860,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>88.98443603515625</v>
+        <v>88.98442840576172</v>
       </c>
       <c r="C170" t="n">
         <v>99.80000305175781</v>
@@ -4877,11 +4889,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>79.00031280517578</v>
+        <v>79.00028991699219</v>
       </c>
       <c r="C171" t="n">
         <v>88.26000213623047</v>
@@ -4906,11 +4918,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>45.1302375793457</v>
+        <v>45.13025283813477</v>
       </c>
       <c r="C172" t="n">
         <v>50.41999816894531</v>
@@ -4935,11 +4947,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>57.96577072143555</v>
+        <v>57.96577835083008</v>
       </c>
       <c r="C173" t="n">
         <v>64.76000213623047</v>
@@ -4964,7 +4976,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4993,7 +5005,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5022,11 +5034,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>57.48455810546875</v>
+        <v>57.48456573486328</v>
       </c>
       <c r="C176" t="n">
         <v>63.79999923706055</v>
@@ -5051,11 +5063,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>62.29486083984375</v>
+        <v>62.29488754272461</v>
       </c>
       <c r="C177" t="n">
         <v>69.02999877929688</v>
@@ -5078,7 +5090,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5105,11 +5117,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>65.94971466064453</v>
+        <v>65.94972991943359</v>
       </c>
       <c r="C179" t="n">
         <v>73.08000183105469</v>
@@ -5132,11 +5144,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>77.38258361816406</v>
+        <v>77.38259887695312</v>
       </c>
       <c r="C180" t="n">
         <v>85.63999938964844</v>
@@ -5161,11 +5173,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>89.31886291503906</v>
+        <v>89.31887054443359</v>
       </c>
       <c r="C181" t="n">
         <v>98.84999847412109</v>
@@ -5190,7 +5202,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5219,11 +5231,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>108.9714508056641</v>
+        <v>108.9714584350586</v>
       </c>
       <c r="C183" t="n">
         <v>120.1900024414062</v>
@@ -5248,11 +5260,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>115.3543548583984</v>
+        <v>115.3543395996094</v>
       </c>
       <c r="C184" t="n">
         <v>127.2300033569336</v>
@@ -5277,11 +5289,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>135.1648559570312</v>
+        <v>135.1648712158203</v>
       </c>
       <c r="C185" t="n">
         <v>149.0800018310547</v>
@@ -5306,11 +5318,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>146.1468200683594</v>
+        <v>146.1468353271484</v>
       </c>
       <c r="C186" t="n">
         <v>160.7799987792969</v>
@@ -5335,11 +5347,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>140.6110992431641</v>
+        <v>140.6111145019531</v>
       </c>
       <c r="C187" t="n">
         <v>154.6900024414062</v>
@@ -5364,7 +5376,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5393,11 +5405,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>151.9820404052734</v>
+        <v>151.9821014404297</v>
       </c>
       <c r="C189" t="n">
         <v>165.9700012207031</v>
@@ -5422,11 +5434,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>148.3192291259766</v>
+        <v>148.3191986083984</v>
       </c>
       <c r="C190" t="n">
         <v>161.9700012207031</v>
@@ -5451,11 +5463,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>138.3011932373047</v>
+        <v>138.3011779785156</v>
       </c>
       <c r="C191" t="n">
         <v>151.0299987792969</v>
@@ -5480,7 +5492,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5509,7 +5521,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5538,7 +5550,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5567,11 +5579,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>141.4290618896484</v>
+        <v>141.4290924072266</v>
       </c>
       <c r="C195" t="n">
         <v>153.2700042724609</v>
@@ -5596,11 +5608,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>121.1471252441406</v>
+        <v>121.1471633911133</v>
       </c>
       <c r="C196" t="n">
         <v>131.2899932861328</v>
@@ -5625,11 +5637,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>114.992431640625</v>
+        <v>114.9924392700195</v>
       </c>
       <c r="C197" t="n">
         <v>124.620002746582</v>
@@ -5654,11 +5666,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>118.6055679321289</v>
+        <v>118.6055603027344</v>
       </c>
       <c r="C198" t="n">
         <v>127.8600006103516</v>
@@ -5683,11 +5695,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>96.64878082275391</v>
+        <v>96.64878845214844</v>
       </c>
       <c r="C199" t="n">
         <v>104.1900024414062</v>
@@ -5712,11 +5724,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>101.8805694580078</v>
+        <v>101.8805465698242</v>
       </c>
       <c r="C200" t="n">
         <v>109.8300018310547</v>
@@ -5741,11 +5753,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>98.71491241455078</v>
+        <v>98.71489715576172</v>
       </c>
       <c r="C201" t="n">
         <v>105.8199996948242</v>
@@ -5770,11 +5782,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>85.98140716552734</v>
+        <v>85.98139190673828</v>
       </c>
       <c r="C202" t="n">
         <v>92.16999816894531</v>
@@ -5799,11 +5811,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>98.90146636962891</v>
+        <v>98.9014892578125</v>
       </c>
       <c r="C203" t="n">
         <v>106.0199966430664</v>
@@ -5828,11 +5840,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>96.88100433349609</v>
+        <v>96.88099670410156</v>
       </c>
       <c r="C204" t="n">
         <v>103.2399978637695</v>
@@ -5857,11 +5869,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>87.23420715332031</v>
+        <v>87.23419952392578</v>
       </c>
       <c r="C205" t="n">
         <v>92.95999908447266</v>
@@ -5886,11 +5898,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>111.6702728271484</v>
+        <v>111.670280456543</v>
       </c>
       <c r="C206" t="n">
         <v>119</v>
@@ -5915,11 +5927,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>102.8679504394531</v>
+        <v>102.8679428100586</v>
       </c>
       <c r="C207" t="n">
         <v>109.0800018310547</v>
@@ -5944,11 +5956,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>90.68374633789062</v>
+        <v>90.68375396728516</v>
       </c>
       <c r="C208" t="n">
         <v>96.16000366210938</v>
@@ -5973,11 +5985,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>91.75882720947266</v>
+        <v>91.75881958007812</v>
       </c>
       <c r="C209" t="n">
         <v>97.30000305175781</v>
@@ -6002,11 +6014,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>98.95446014404297</v>
+        <v>98.9544677734375</v>
       </c>
       <c r="C210" t="n">
         <v>104.2099990844727</v>
@@ -6031,11 +6043,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>103.8542404174805</v>
+        <v>103.8542251586914</v>
       </c>
       <c r="C211" t="n">
         <v>109.370002746582</v>
@@ -6060,7 +6072,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6089,11 +6101,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>97.74561309814453</v>
+        <v>97.74562072753906</v>
       </c>
       <c r="C213" t="n">
         <v>102.3899993896484</v>
@@ -6118,7 +6130,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6147,11 +6159,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>96.69551086425781</v>
+        <v>96.69551849365234</v>
       </c>
       <c r="C215" t="n">
         <v>101.2900009155273</v>
@@ -6176,11 +6188,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>107.2107543945312</v>
+        <v>107.2107620239258</v>
       </c>
       <c r="C216" t="n">
         <v>111.6600036621094</v>
@@ -6205,7 +6217,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6234,11 +6246,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>129.9280242919922</v>
+        <v>129.9279937744141</v>
       </c>
       <c r="C218" t="n">
         <v>135.3200073242188</v>
@@ -6263,11 +6275,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>132.7149505615234</v>
+        <v>132.7149353027344</v>
       </c>
       <c r="C219" t="n">
         <v>137.6100006103516</v>
@@ -6292,7 +6304,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6321,7 +6333,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6350,11 +6362,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>133.2955322265625</v>
+        <v>133.2955169677734</v>
       </c>
       <c r="C222" t="n">
         <v>137.6300048828125</v>
@@ -6379,11 +6391,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>134.0896759033203</v>
+        <v>134.0897064208984</v>
       </c>
       <c r="C223" t="n">
         <v>138.4499969482422</v>
@@ -6408,11 +6420,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>146.6318359375</v>
+        <v>146.6318206787109</v>
       </c>
       <c r="C224" t="n">
         <v>151.3999938964844</v>
@@ -6437,7 +6449,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6466,11 +6478,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>145.6627197265625</v>
+        <v>145.6627044677734</v>
       </c>
       <c r="C226" t="n">
         <v>149.7299957275391</v>
@@ -6495,11 +6507,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>158.3679656982422</v>
+        <v>158.3679504394531</v>
       </c>
       <c r="C227" t="n">
         <v>162.7899932861328</v>
@@ -6524,7 +6536,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6553,7 +6565,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6582,7 +6594,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6611,7 +6623,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6640,7 +6652,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6669,11 +6681,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>176.4560852050781</v>
+        <v>176.4561004638672</v>
       </c>
       <c r="C233" t="n">
         <v>180.2599945068359</v>
@@ -6698,7 +6710,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6727,7 +6739,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6756,11 +6768,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>211.1348266601562</v>
+        <v>211.1348114013672</v>
       </c>
       <c r="C236" t="n">
         <v>215</v>
@@ -6785,7 +6797,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6814,7 +6826,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6872,11 +6884,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>216.5375366210938</v>
+        <v>216.5375213623047</v>
       </c>
       <c r="C240" t="n">
         <v>219.0700073242188</v>
@@ -6901,7 +6913,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6930,11 +6942,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>216.3991394042969</v>
+        <v>216.3991241455078</v>
       </c>
       <c r="C242" t="n">
         <v>218.9299926757812</v>
@@ -6959,7 +6971,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6988,7 +7000,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7017,7 +7029,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7046,7 +7058,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7075,7 +7087,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7104,7 +7116,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7133,7 +7145,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7162,32 +7174,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>196.1000061035156</v>
+        <v>196.6100006103516</v>
       </c>
       <c r="C250" t="n">
-        <v>196.1000061035156</v>
+        <v>196.6100006103516</v>
       </c>
       <c r="D250" t="n">
-        <v>57909000</v>
+        <v>61597000</v>
       </c>
       <c r="E250" t="n">
         <v>17.23</v>
       </c>
       <c r="F250" t="n">
-        <v>11.38131201993706</v>
+        <v>11.41091123681669</v>
       </c>
       <c r="G250" t="n">
         <v>613484836</v>
       </c>
       <c r="H250" t="n">
-        <v>120304380084.0143</v>
+        <v>120617253980.4014</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09439353118746036</v>
+        <v>0.1004050897192836</v>
       </c>
     </row>
   </sheetData>
@@ -7219,75 +7231,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7323,13 +7335,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7365,13 +7377,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7407,13 +7419,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7449,13 +7461,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7491,13 +7503,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40609</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I10" t="n">
         <v>6.01</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40609</v>
       </c>
       <c r="K10" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40542</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I11" t="n">
         <v>6.82</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="K11" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I12" t="n">
         <v>7.46</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K12" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I13" t="n">
         <v>7.469999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="K13" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I14" t="n">
         <v>6.8</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K14" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I15" t="n">
         <v>7.31</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="K15" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I16" t="n">
         <v>5.500000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="K16" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I17" t="n">
         <v>5.740000000000001</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="K17" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I18" t="n">
         <v>6.16</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K18" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I19" t="n">
         <v>5.23</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="K19" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I20" t="n">
         <v>6.94</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="K20" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I21" t="n">
         <v>6.79</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="K21" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I22" t="n">
         <v>6.96</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K22" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I23" t="n">
         <v>7.13</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="K23" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I24" t="n">
         <v>7.3</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K24" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I25" t="n">
         <v>7.3</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K25" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I26" t="n">
         <v>7.59</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K26" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I27" t="n">
         <v>7.63</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="K27" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I28" t="n">
         <v>7.09</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="K28" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I29" t="n">
         <v>7.209999999999999</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="K29" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I30" t="n">
         <v>7.06</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K30" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I31" t="n">
         <v>6.9</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K31" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I32" t="n">
         <v>7.09</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="K32" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I33" t="n">
         <v>7.01</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K33" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I34" t="n">
         <v>6.879999999999999</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K34" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I35" t="n">
         <v>6.58</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K35" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I36" t="n">
         <v>6.83</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K36" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I37" t="n">
         <v>7.07</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="K37" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I38" t="n">
         <v>3.490000000000001</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="K38" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I39" t="n">
         <v>4.57</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K39" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I40" t="n">
         <v>6.34</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K40" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I41" t="n">
         <v>7.19</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K41" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I42" t="n">
         <v>11.82</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="K42" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I43" t="n">
         <v>12.06</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="K43" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I44" t="n">
         <v>11.59</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K44" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I45" t="n">
         <v>11.29</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K45" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I46" t="n">
         <v>11.05</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K46" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I47" t="n">
         <v>5.090000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K47" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I48" t="n">
         <v>-0.3599999999999985</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K48" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I49" t="n">
         <v>2.010000000000001</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="K49" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I50" t="n">
         <v>5.18</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K50" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I51" t="n">
         <v>15.31</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="K51" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I52" t="n">
         <v>25.14</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K52" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I53" t="n">
         <v>26.86</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="K53" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I54" t="n">
         <v>26.94</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="K54" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I55" t="n">
         <v>25.53</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="K55" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I56" t="n">
         <v>22.87</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K56" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I57" t="n">
         <v>20.29</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="K57" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I58" t="n">
         <v>17.91</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K58" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I59" t="n">
         <v>14.6</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="K59" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I60" t="n">
         <v>13.16</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K60" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I61" t="n">
         <v>13.41</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K61" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I62" t="n">
         <v>11.95</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="K62" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I63" t="n">
         <v>12.77</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I64" t="n">
         <v>10.63</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K64" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I65" t="n">
         <v>10.59</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K65" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I66" t="n">
         <v>11.59</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="K66" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I67" t="n">
         <v>11.91</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K67" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I68" t="n">
         <v>1.950000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K68" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I69" t="n">
         <v>2.370000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="K69" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I70" t="n">
         <v>4.030000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K70" t="n">
@@ -10423,13 +10435,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10456,7 +10468,7 @@
       <c r="I71" t="n">
         <v>3.920000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K71" t="n">
@@ -10469,13 +10481,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10502,7 +10514,7 @@
       <c r="I72" t="n">
         <v>17.23</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="K72" t="n">
@@ -10539,52 +10551,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10613,10 +10625,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="C3" t="n">
@@ -10645,10 +10657,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C7" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40609</v>
       </c>
       <c r="C8" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40673</v>
       </c>
       <c r="C9" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="C11" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C12" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C13" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41130</v>
       </c>
       <c r="C14" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41221</v>
       </c>
       <c r="C15" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41403</v>
       </c>
       <c r="C17" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41494</v>
       </c>
       <c r="C18" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41584</v>
       </c>
       <c r="C19" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C20" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="C21" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C23" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="C24" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="C25" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42219</v>
       </c>
       <c r="C26" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42310</v>
       </c>
       <c r="C27" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C28" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42573</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C30" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="C35" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43152</v>
       </c>
       <c r="C36" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C37" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C38" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C39" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43516</v>
       </c>
       <c r="C40" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="C41" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C42" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C43" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C44" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C46" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44137</v>
       </c>
       <c r="C47" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C48" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C49" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C50" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="C51" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="C52" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44691</v>
       </c>
       <c r="C53" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C54" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="C55" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C56" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="C57" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C58" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="C60" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C63" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="C64" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C65" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C66" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="C67" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C68" t="n">
@@ -12725,10 +12737,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C69" t="n">
@@ -12757,10 +12769,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46231</v>
       </c>
       <c r="C70" t="n">
@@ -12807,12 +12819,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/COF.xlsx
+++ b/salidas/empresas/COF.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>60.36521530151367</v>
+        <v>60.3652229309082</v>
       </c>
       <c r="C2" t="n">
         <v>83.30000305175781</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>63.50231170654297</v>
+        <v>63.50229644775391</v>
       </c>
       <c r="C3" t="n">
         <v>87.59999847412109</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>58.36990737915039</v>
+        <v>58.36990356445312</v>
       </c>
       <c r="C4" t="n">
         <v>80.51999664306641</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>62.80640411376953</v>
+        <v>62.80640029907227</v>
       </c>
       <c r="C5" t="n">
         <v>86.63999938964844</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>60.01985931396484</v>
+        <v>60.01984405517578</v>
       </c>
       <c r="C6" t="n">
         <v>82.76999664306641</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>61.96324157714844</v>
+        <v>61.96321487426758</v>
       </c>
       <c r="C7" t="n">
         <v>85.44999694824219</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>53.02598190307617</v>
+        <v>53.02598571777344</v>
       </c>
       <c r="C9" t="n">
         <v>73.09999847412109</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>57.05916213989258</v>
+        <v>57.05918502807617</v>
       </c>
       <c r="C10" t="n">
         <v>78.66000366210938</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>57.54516983032227</v>
+        <v>57.545166015625</v>
       </c>
       <c r="C11" t="n">
         <v>79.33000183105469</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>56.51301574707031</v>
+        <v>56.51300811767578</v>
       </c>
       <c r="C12" t="n">
         <v>77.87999725341797</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>55.74385070800781</v>
+        <v>55.74385833740234</v>
       </c>
       <c r="C13" t="n">
         <v>76.81999969482422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>58.34164428710938</v>
+        <v>58.34164810180664</v>
       </c>
       <c r="C14" t="n">
         <v>80.40000152587891</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>55.9142951965332</v>
+        <v>55.91429138183594</v>
       </c>
       <c r="C15" t="n">
         <v>77.02999877929688</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>54.77465057373047</v>
+        <v>54.77467727661133</v>
       </c>
       <c r="C16" t="n">
         <v>75.45999908447266</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>53.90361785888672</v>
+        <v>53.90361404418945</v>
       </c>
       <c r="C17" t="n">
         <v>74.26000213623047</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>57.93122100830078</v>
+        <v>57.93121337890625</v>
       </c>
       <c r="C18" t="n">
         <v>79.77999877929688</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>56.95820617675781</v>
+        <v>56.95819854736328</v>
       </c>
       <c r="C19" t="n">
         <v>78.44000244140625</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>51.3814811706543</v>
+        <v>51.38147354125977</v>
       </c>
       <c r="C20" t="n">
         <v>70.76000213623047</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>46.96997451782227</v>
+        <v>46.96998977661133</v>
       </c>
       <c r="C21" t="n">
         <v>64.66000366210938</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>48.25574493408203</v>
+        <v>48.25574111938477</v>
       </c>
       <c r="C22" t="n">
         <v>66.43000030517578</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>47.64554977416992</v>
+        <v>47.64554595947266</v>
       </c>
       <c r="C23" t="n">
         <v>65.58999633789062</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>38.74276733398438</v>
+        <v>38.74277877807617</v>
       </c>
       <c r="C24" t="n">
         <v>53.31000137329102</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>34.34595489501953</v>
+        <v>34.3459587097168</v>
       </c>
       <c r="C25" t="n">
         <v>47.2599983215332</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>39.69478607177734</v>
+        <v>39.69480514526367</v>
       </c>
       <c r="C26" t="n">
         <v>54.61999893188477</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>36.04309463500977</v>
+        <v>36.04311370849609</v>
       </c>
       <c r="C28" t="n">
         <v>49.22000122070312</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>38.81112670898438</v>
+        <v>38.81116104125977</v>
       </c>
       <c r="C29" t="n">
         <v>53</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>35.48309326171875</v>
+        <v>35.48307800292969</v>
       </c>
       <c r="C30" t="n">
         <v>48.11999893188477</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>30.86703300476074</v>
+        <v>30.8670539855957</v>
       </c>
       <c r="C32" t="n">
         <v>41.86000061035156</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>32.82173919677734</v>
+        <v>32.82175064086914</v>
       </c>
       <c r="C33" t="n">
         <v>44.13999938964844</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>37.92272186279297</v>
+        <v>37.92272567749023</v>
       </c>
       <c r="C34" t="n">
         <v>51</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>29.08894157409668</v>
+        <v>29.08895683288574</v>
       </c>
       <c r="C35" t="n">
         <v>39.11999893188477</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>25.84014701843262</v>
+        <v>25.84014511108398</v>
       </c>
       <c r="C36" t="n">
         <v>34.40999984741211</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>23.94775772094727</v>
+        <v>23.94775581359863</v>
       </c>
       <c r="C37" t="n">
         <v>31.88999938964844</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>11.89503383636475</v>
+        <v>11.89503002166748</v>
       </c>
       <c r="C38" t="n">
         <v>15.84000015258789</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>9.294203758239746</v>
+        <v>9.294205665588379</v>
       </c>
       <c r="C39" t="n">
         <v>12.05000019073486</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>9.440751075744629</v>
+        <v>9.440753936767578</v>
       </c>
       <c r="C40" t="n">
         <v>12.23999977111816</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>12.91161823272705</v>
+        <v>12.91161727905273</v>
       </c>
       <c r="C41" t="n">
         <v>16.73999977111816</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>18.89285087585449</v>
+        <v>18.89284706115723</v>
       </c>
       <c r="C42" t="n">
         <v>24.44000053405762</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>16.91388320922852</v>
+        <v>16.91388893127441</v>
       </c>
       <c r="C43" t="n">
         <v>21.8799991607666</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>23.73200988769531</v>
+        <v>23.73202133178711</v>
       </c>
       <c r="C44" t="n">
         <v>30.70000076293945</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>28.87116050720215</v>
+        <v>28.87115287780762</v>
       </c>
       <c r="C45" t="n">
         <v>37.29000091552734</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>27.6633415222168</v>
+        <v>27.66335105895996</v>
       </c>
       <c r="C46" t="n">
         <v>35.72999954223633</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>28.33692741394043</v>
+        <v>28.33692169189453</v>
       </c>
       <c r="C47" t="n">
         <v>36.59999847412109</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>29.72274398803711</v>
+        <v>29.72274589538574</v>
       </c>
       <c r="C49" t="n">
         <v>38.34000015258789</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>28.57538604736328</v>
+        <v>28.57537460327148</v>
       </c>
       <c r="C50" t="n">
         <v>36.86000061035156</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>29.30683326721191</v>
+        <v>29.30681419372559</v>
       </c>
       <c r="C51" t="n">
         <v>37.75</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>32.14820861816406</v>
+        <v>32.14822006225586</v>
       </c>
       <c r="C52" t="n">
         <v>41.40999984741211</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>33.70089721679688</v>
+        <v>33.70090866088867</v>
       </c>
       <c r="C53" t="n">
         <v>43.40999984741211</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>32.10005950927734</v>
+        <v>32.10005187988281</v>
       </c>
       <c r="C54" t="n">
         <v>41.29999923706055</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>31.32279777526855</v>
+        <v>31.32281112670898</v>
       </c>
       <c r="C55" t="n">
         <v>40.29999923706055</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>32.90061569213867</v>
+        <v>32.90060424804688</v>
       </c>
       <c r="C56" t="n">
         <v>42.33000183105469</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>29.47012138366699</v>
+        <v>29.47011756896973</v>
       </c>
       <c r="C57" t="n">
         <v>37.86999893188477</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>30.77747535705566</v>
+        <v>30.77747344970703</v>
       </c>
       <c r="C58" t="n">
         <v>39.54999923706055</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>29.00320625305176</v>
+        <v>29.00320053100586</v>
       </c>
       <c r="C59" t="n">
         <v>37.27000045776367</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>29.00827789306641</v>
+        <v>29.00825881958008</v>
       </c>
       <c r="C60" t="n">
         <v>37.22999954223633</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>33.16121292114258</v>
+        <v>33.16119766235352</v>
       </c>
       <c r="C61" t="n">
         <v>42.56000137329102</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>37.52455139160156</v>
+        <v>37.52451705932617</v>
       </c>
       <c r="C62" t="n">
         <v>48.15999984741211</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>38.81661224365234</v>
+        <v>38.81660079956055</v>
       </c>
       <c r="C63" t="n">
         <v>49.77000045776367</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>40.52464294433594</v>
+        <v>40.52463150024414</v>
       </c>
       <c r="C64" t="n">
         <v>51.95999908447266</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>42.68501281738281</v>
+        <v>42.68499755859375</v>
       </c>
       <c r="C65" t="n">
         <v>54.72999954223633</v>
@@ -1848,7 +1848,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>42.41915512084961</v>
+        <v>42.41915893554688</v>
       </c>
       <c r="C66" t="n">
         <v>54.34000015258789</v>
@@ -1877,7 +1877,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>40.33488082885742</v>
+        <v>40.33489227294922</v>
       </c>
       <c r="C67" t="n">
         <v>51.66999816894531</v>
@@ -1906,7 +1906,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>37.31385803222656</v>
+        <v>37.31386566162109</v>
       </c>
       <c r="C68" t="n">
         <v>47.79999923706055</v>
@@ -1935,7 +1935,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>35.99185943603516</v>
+        <v>35.99184799194336</v>
       </c>
       <c r="C69" t="n">
         <v>46.04999923706055</v>
@@ -1964,7 +1964,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>30.9741039276123</v>
+        <v>30.97409057617188</v>
       </c>
       <c r="C70" t="n">
         <v>39.63000106811523</v>
@@ -1993,7 +1993,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>35.68703460693359</v>
+        <v>35.68703079223633</v>
       </c>
       <c r="C71" t="n">
         <v>45.65999984741211</v>
@@ -2022,7 +2022,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>34.94698715209961</v>
+        <v>34.94699478149414</v>
       </c>
       <c r="C72" t="n">
         <v>44.65999984741211</v>
@@ -2051,7 +2051,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>33.09245300292969</v>
+        <v>33.09244155883789</v>
       </c>
       <c r="C73" t="n">
         <v>42.29000091552734</v>
@@ -2080,7 +2080,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>35.7999267578125</v>
+        <v>35.79993057250977</v>
       </c>
       <c r="C74" t="n">
         <v>45.75</v>
@@ -2167,7 +2167,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>43.4597282409668</v>
+        <v>43.45972442626953</v>
       </c>
       <c r="C77" t="n">
         <v>55.47999954223633</v>
@@ -2225,7 +2225,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>42.85916900634766</v>
+        <v>42.85918426513672</v>
       </c>
       <c r="C79" t="n">
         <v>54.65999984741211</v>
@@ -2254,7 +2254,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>44.29409408569336</v>
+        <v>44.29407501220703</v>
       </c>
       <c r="C80" t="n">
         <v>56.4900016784668</v>
@@ -2283,7 +2283,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.36464691162109</v>
+        <v>44.36465072631836</v>
       </c>
       <c r="C81" t="n">
         <v>56.52999877929688</v>
@@ -2312,7 +2312,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>44.74134063720703</v>
+        <v>44.74135971069336</v>
       </c>
       <c r="C82" t="n">
         <v>57.0099983215332</v>
@@ -2341,7 +2341,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>47.2213134765625</v>
+        <v>47.22132110595703</v>
       </c>
       <c r="C83" t="n">
         <v>60.16999816894531</v>
@@ -2370,7 +2370,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.2414436340332</v>
+        <v>45.24142074584961</v>
       </c>
       <c r="C84" t="n">
         <v>57.59999847412109</v>
@@ -2399,7 +2399,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>45.5006103515625</v>
+        <v>45.5006217956543</v>
       </c>
       <c r="C85" t="n">
         <v>57.93000030517578</v>
@@ -2457,7 +2457,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>40.11597442626953</v>
+        <v>40.11598968505859</v>
       </c>
       <c r="C87" t="n">
         <v>51.02999877929688</v>
@@ -2486,7 +2486,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.19759750366211</v>
+        <v>43.19758224487305</v>
       </c>
       <c r="C88" t="n">
         <v>54.95000076293945</v>
@@ -2515,7 +2515,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>45.42231750488281</v>
+        <v>45.42232513427734</v>
       </c>
       <c r="C89" t="n">
         <v>57.77999877929688</v>
@@ -2544,7 +2544,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>48.13995742797852</v>
+        <v>48.13996124267578</v>
       </c>
       <c r="C90" t="n">
         <v>60.93000030517578</v>
@@ -2573,7 +2573,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>49.62532806396484</v>
+        <v>49.62532043457031</v>
       </c>
       <c r="C91" t="n">
         <v>62.81000137329102</v>
@@ -2602,7 +2602,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>54.53176498413086</v>
+        <v>54.53176116943359</v>
       </c>
       <c r="C92" t="n">
         <v>69.01999664306641</v>
@@ -2631,7 +2631,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>51.22272109985352</v>
+        <v>51.22271347045898</v>
       </c>
       <c r="C93" t="n">
         <v>64.55000305175781</v>
@@ -2689,7 +2689,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>54.4920768737793</v>
+        <v>54.49207305908203</v>
       </c>
       <c r="C95" t="n">
         <v>68.66999816894531</v>
@@ -2718,7 +2718,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>57.08573532104492</v>
+        <v>57.08572387695312</v>
       </c>
       <c r="C96" t="n">
         <v>71.62999725341797</v>
@@ -2747,7 +2747,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>61.05458831787109</v>
+        <v>61.05458068847656</v>
       </c>
       <c r="C97" t="n">
         <v>76.61000061035156</v>
@@ -2805,7 +2805,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>58.77705383300781</v>
+        <v>58.77708053588867</v>
       </c>
       <c r="C99" t="n">
         <v>73.43000030517578</v>
@@ -2834,7 +2834,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>61.76276397705078</v>
+        <v>61.76275253295898</v>
       </c>
       <c r="C100" t="n">
         <v>77.16000366210938</v>
@@ -2863,7 +2863,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>59.15329360961914</v>
+        <v>59.15327835083008</v>
       </c>
       <c r="C101" t="n">
         <v>73.90000152587891</v>
@@ -2892,7 +2892,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>63.39640808105469</v>
+        <v>63.39643478393555</v>
       </c>
       <c r="C102" t="n">
         <v>78.88999938964844</v>
@@ -2921,7 +2921,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>66.37778472900391</v>
+        <v>66.37779998779297</v>
       </c>
       <c r="C103" t="n">
         <v>82.59999847412109</v>
@@ -2950,7 +2950,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>63.91875457763672</v>
+        <v>63.91874694824219</v>
       </c>
       <c r="C104" t="n">
         <v>79.54000091552734</v>
@@ -2979,7 +2979,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>66.19595336914062</v>
+        <v>66.19598388671875</v>
       </c>
       <c r="C105" t="n">
         <v>82.05999755859375</v>
@@ -3008,7 +3008,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>65.84103393554688</v>
+        <v>65.841064453125</v>
       </c>
       <c r="C106" t="n">
         <v>81.62000274658203</v>
@@ -3037,7 +3037,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>66.76871490478516</v>
+        <v>66.76872253417969</v>
       </c>
       <c r="C107" t="n">
         <v>82.76999664306641</v>
@@ -3066,7 +3066,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>67.36322784423828</v>
+        <v>67.36325073242188</v>
       </c>
       <c r="C108" t="n">
         <v>83.19999694824219</v>
@@ -3095,7 +3095,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>66.83697509765625</v>
+        <v>66.83699035644531</v>
       </c>
       <c r="C109" t="n">
         <v>82.55000305175781</v>
@@ -3124,7 +3124,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>59.27480697631836</v>
+        <v>59.27480316162109</v>
       </c>
       <c r="C110" t="n">
         <v>73.20999908447266</v>
@@ -3153,7 +3153,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>63.98282623291016</v>
+        <v>63.98283767700195</v>
       </c>
       <c r="C111" t="n">
         <v>78.70999908447266</v>
@@ -3182,7 +3182,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>64.07223510742188</v>
+        <v>64.07221984863281</v>
       </c>
       <c r="C112" t="n">
         <v>78.81999969482422</v>
@@ -3211,7 +3211,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>65.72238159179688</v>
+        <v>65.72241973876953</v>
       </c>
       <c r="C113" t="n">
         <v>80.84999847412109</v>
@@ -3327,7 +3327,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>63.82167434692383</v>
+        <v>63.82170104980469</v>
       </c>
       <c r="C117" t="n">
         <v>77.75</v>
@@ -3414,7 +3414,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>64.76719665527344</v>
+        <v>64.76715850830078</v>
       </c>
       <c r="C120" t="n">
         <v>78.51000213623047</v>
@@ -3472,7 +3472,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>54.13350677490234</v>
+        <v>54.13352584838867</v>
       </c>
       <c r="C122" t="n">
         <v>65.62000274658203</v>
@@ -3501,7 +3501,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>54.57499313354492</v>
+        <v>54.57500076293945</v>
       </c>
       <c r="C123" t="n">
         <v>65.73000335693359</v>
@@ -3530,7 +3530,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>57.54742431640625</v>
+        <v>57.54742813110352</v>
       </c>
       <c r="C124" t="n">
         <v>69.30999755859375</v>
@@ -3559,7 +3559,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>60.10474014282227</v>
+        <v>60.1047477722168</v>
       </c>
       <c r="C125" t="n">
         <v>72.38999938964844</v>
@@ -3588,7 +3588,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>61.15821838378906</v>
+        <v>61.15822219848633</v>
       </c>
       <c r="C126" t="n">
         <v>73.23999786376953</v>
@@ -3617,7 +3617,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>53.03327941894531</v>
+        <v>53.03330230712891</v>
       </c>
       <c r="C127" t="n">
         <v>63.5099983215332</v>
@@ -3646,7 +3646,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>56.01436996459961</v>
+        <v>56.01437759399414</v>
       </c>
       <c r="C128" t="n">
         <v>67.08000183105469</v>
@@ -3675,7 +3675,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>60.15028762817383</v>
+        <v>60.15030670166016</v>
       </c>
       <c r="C129" t="n">
         <v>71.59999847412109</v>
@@ -3704,7 +3704,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>60.34353256225586</v>
+        <v>60.34351348876953</v>
       </c>
       <c r="C130" t="n">
         <v>71.83000183105469</v>
@@ -3733,7 +3733,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>62.20009613037109</v>
+        <v>62.20008087158203</v>
       </c>
       <c r="C131" t="n">
         <v>74.04000091552734</v>
@@ -3791,7 +3791,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>73.6939697265625</v>
+        <v>73.69396209716797</v>
       </c>
       <c r="C133" t="n">
         <v>87.23999786376953</v>
@@ -3849,7 +3849,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>79.64997863769531</v>
+        <v>79.64998626708984</v>
       </c>
       <c r="C135" t="n">
         <v>93.86000061035156</v>
@@ -3878,7 +3878,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>73.54003143310547</v>
+        <v>73.54005432128906</v>
       </c>
       <c r="C136" t="n">
         <v>86.66000366210938</v>
@@ -3907,7 +3907,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>68.21078491210938</v>
+        <v>68.21079254150391</v>
       </c>
       <c r="C137" t="n">
         <v>80.37999725341797</v>
@@ -3936,7 +3936,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>65.59589385986328</v>
+        <v>65.59590911865234</v>
       </c>
       <c r="C138" t="n">
         <v>76.91999816894531</v>
@@ -3965,7 +3965,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>70.45677185058594</v>
+        <v>70.45674133300781</v>
       </c>
       <c r="C139" t="n">
         <v>82.62000274658203</v>
@@ -3994,7 +3994,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>73.49265289306641</v>
+        <v>73.49267578125</v>
       </c>
       <c r="C140" t="n">
         <v>86.18000030517578</v>
@@ -4023,7 +4023,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>68.20820617675781</v>
+        <v>68.20822906494141</v>
       </c>
       <c r="C141" t="n">
         <v>79.61000061035156</v>
@@ -4052,7 +4052,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>72.53497314453125</v>
+        <v>72.53493499755859</v>
       </c>
       <c r="C142" t="n">
         <v>84.66000366210938</v>
@@ -4081,7 +4081,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>78.97793579101562</v>
+        <v>78.97794342041016</v>
       </c>
       <c r="C143" t="n">
         <v>92.18000030517578</v>
@@ -4110,7 +4110,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>79.18317413330078</v>
+        <v>79.18318939208984</v>
       </c>
       <c r="C144" t="n">
         <v>92</v>
@@ -4139,7 +4139,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>85.70718383789062</v>
+        <v>85.70719909667969</v>
       </c>
       <c r="C145" t="n">
         <v>99.58000183105469</v>
@@ -4168,7 +4168,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>89.47701263427734</v>
+        <v>89.47700500488281</v>
       </c>
       <c r="C146" t="n">
         <v>103.9599990844727</v>
@@ -4197,7 +4197,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>84.65589904785156</v>
+        <v>84.65592193603516</v>
       </c>
       <c r="C147" t="n">
         <v>97.93000030517578</v>
@@ -4226,7 +4226,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>82.83191680908203</v>
+        <v>82.83193206787109</v>
       </c>
       <c r="C148" t="n">
         <v>95.81999969482422</v>
@@ -4255,7 +4255,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>78.33675384521484</v>
+        <v>78.33679962158203</v>
       </c>
       <c r="C149" t="n">
         <v>90.62000274658203</v>
@@ -4284,7 +4284,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>81.61087036132812</v>
+        <v>81.61089324951172</v>
       </c>
       <c r="C150" t="n">
         <v>94</v>
@@ -4313,7 +4313,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>79.78766632080078</v>
+        <v>79.78765869140625</v>
       </c>
       <c r="C151" t="n">
         <v>91.90000152587891</v>
@@ -4342,7 +4342,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>81.88870239257812</v>
+        <v>81.88872528076172</v>
       </c>
       <c r="C152" t="n">
         <v>94.31999969482422</v>
@@ -4371,7 +4371,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>86.390869140625</v>
+        <v>86.39085388183594</v>
       </c>
       <c r="C153" t="n">
         <v>99.08999633789062</v>
@@ -4400,7 +4400,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>82.76400756835938</v>
+        <v>82.76399993896484</v>
       </c>
       <c r="C154" t="n">
         <v>94.93000030517578</v>
@@ -4429,7 +4429,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>77.85550689697266</v>
+        <v>77.85554504394531</v>
       </c>
       <c r="C155" t="n">
         <v>89.30000305175781</v>
@@ -4458,7 +4458,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>78.53376007080078</v>
+        <v>78.53377532958984</v>
       </c>
       <c r="C156" t="n">
         <v>89.68000030517578</v>
@@ -4516,7 +4516,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>70.57357788085938</v>
+        <v>70.57356262207031</v>
       </c>
       <c r="C158" t="n">
         <v>80.58999633789062</v>
@@ -4545,7 +4545,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>73.56427764892578</v>
+        <v>73.56428527832031</v>
       </c>
       <c r="C159" t="n">
         <v>83.58000183105469</v>
@@ -4574,7 +4574,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>71.90074920654297</v>
+        <v>71.90076446533203</v>
       </c>
       <c r="C160" t="n">
         <v>81.69000244140625</v>
@@ -4603,7 +4603,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>81.70581817626953</v>
+        <v>81.70584106445312</v>
       </c>
       <c r="C161" t="n">
         <v>92.83000183105469</v>
@@ -4632,7 +4632,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>75.91651916503906</v>
+        <v>75.91652679443359</v>
       </c>
       <c r="C162" t="n">
         <v>85.87000274658203</v>
@@ -4661,7 +4661,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>80.22202301025391</v>
+        <v>80.22203063964844</v>
       </c>
       <c r="C163" t="n">
         <v>90.73999786376953</v>
@@ -4690,7 +4690,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>81.707275390625</v>
+        <v>81.70726013183594</v>
       </c>
       <c r="C164" t="n">
         <v>92.41999816894531</v>
@@ -4719,7 +4719,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>76.91656494140625</v>
+        <v>76.91657257080078</v>
       </c>
       <c r="C165" t="n">
         <v>86.62000274658203</v>
@@ -4748,7 +4748,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>80.78814697265625</v>
+        <v>80.78813934326172</v>
       </c>
       <c r="C166" t="n">
         <v>90.98000335693359</v>
@@ -4777,7 +4777,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>82.80386352539062</v>
+        <v>82.80385589599609</v>
       </c>
       <c r="C167" t="n">
         <v>93.25</v>
@@ -4806,7 +4806,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>89.17167663574219</v>
+        <v>89.17166900634766</v>
       </c>
       <c r="C168" t="n">
         <v>100.0100021362305</v>
@@ -4835,7 +4835,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>91.75737762451172</v>
+        <v>91.75740051269531</v>
       </c>
       <c r="C169" t="n">
         <v>102.9100036621094</v>
@@ -4893,7 +4893,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>79.00028991699219</v>
+        <v>79.00030517578125</v>
       </c>
       <c r="C171" t="n">
         <v>88.26000213623047</v>
@@ -4922,7 +4922,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>45.13025283813477</v>
+        <v>45.13024139404297</v>
       </c>
       <c r="C172" t="n">
         <v>50.41999816894531</v>
@@ -4980,7 +4980,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>61.30484771728516</v>
+        <v>61.30483627319336</v>
       </c>
       <c r="C174" t="n">
         <v>68.04000091552734</v>
@@ -5009,7 +5009,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>56.39433670043945</v>
+        <v>56.39434814453125</v>
       </c>
       <c r="C175" t="n">
         <v>62.59000015258789</v>
@@ -5038,7 +5038,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>57.48456573486328</v>
+        <v>57.48455810546875</v>
       </c>
       <c r="C176" t="n">
         <v>63.79999923706055</v>
@@ -5067,7 +5067,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>62.29488754272461</v>
+        <v>62.29486846923828</v>
       </c>
       <c r="C177" t="n">
         <v>69.02999877929688</v>
@@ -5094,7 +5094,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>64.8487548828125</v>
+        <v>64.84873199462891</v>
       </c>
       <c r="C178" t="n">
         <v>71.86000061035156</v>
@@ -5148,7 +5148,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>77.38259887695312</v>
+        <v>77.38259124755859</v>
       </c>
       <c r="C180" t="n">
         <v>85.63999938964844</v>
@@ -5177,7 +5177,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>89.31887054443359</v>
+        <v>89.31888580322266</v>
       </c>
       <c r="C181" t="n">
         <v>98.84999847412109</v>
@@ -5206,7 +5206,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>94.20725250244141</v>
+        <v>94.20724487304688</v>
       </c>
       <c r="C182" t="n">
         <v>104.2600021362305</v>
@@ -5235,7 +5235,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>108.9714584350586</v>
+        <v>108.9714508056641</v>
       </c>
       <c r="C183" t="n">
         <v>120.1900024414062</v>
@@ -5264,7 +5264,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>115.3543395996094</v>
+        <v>115.3543548583984</v>
       </c>
       <c r="C184" t="n">
         <v>127.2300033569336</v>
@@ -5322,7 +5322,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>146.1468353271484</v>
+        <v>146.1467895507812</v>
       </c>
       <c r="C186" t="n">
         <v>160.7799987792969</v>
@@ -5351,7 +5351,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>140.6111145019531</v>
+        <v>140.6111297607422</v>
       </c>
       <c r="C187" t="n">
         <v>154.6900024414062</v>
@@ -5380,7 +5380,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>146.9830932617188</v>
+        <v>146.9831237792969</v>
       </c>
       <c r="C188" t="n">
         <v>161.6999969482422</v>
@@ -5409,7 +5409,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>151.9821014404297</v>
+        <v>151.9820556640625</v>
       </c>
       <c r="C189" t="n">
         <v>165.9700012207031</v>
@@ -5438,7 +5438,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>148.3191986083984</v>
+        <v>148.3191680908203</v>
       </c>
       <c r="C190" t="n">
         <v>161.9700012207031</v>
@@ -5467,7 +5467,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>138.3011779785156</v>
+        <v>138.3011932373047</v>
       </c>
       <c r="C191" t="n">
         <v>151.0299987792969</v>
@@ -5496,7 +5496,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>129.1793670654297</v>
+        <v>129.1793975830078</v>
       </c>
       <c r="C192" t="n">
         <v>140.5299987792969</v>
@@ -5525,7 +5525,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>133.3710174560547</v>
+        <v>133.3710479736328</v>
       </c>
       <c r="C193" t="n">
         <v>145.0899963378906</v>
@@ -5554,7 +5554,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>134.8785705566406</v>
+        <v>134.8785858154297</v>
       </c>
       <c r="C194" t="n">
         <v>146.7299957275391</v>
@@ -5612,7 +5612,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>121.1471633911133</v>
+        <v>121.1471328735352</v>
       </c>
       <c r="C196" t="n">
         <v>131.2899932861328</v>
@@ -5641,7 +5641,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>114.9924392700195</v>
+        <v>114.9924545288086</v>
       </c>
       <c r="C197" t="n">
         <v>124.620002746582</v>
@@ -5670,7 +5670,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>118.6055603027344</v>
+        <v>118.6055526733398</v>
       </c>
       <c r="C198" t="n">
         <v>127.8600006103516</v>
@@ -5728,7 +5728,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>101.8805465698242</v>
+        <v>101.8805694580078</v>
       </c>
       <c r="C200" t="n">
         <v>109.8300018310547</v>
@@ -5757,7 +5757,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>98.71489715576172</v>
+        <v>98.71492004394531</v>
       </c>
       <c r="C201" t="n">
         <v>105.8199996948242</v>
@@ -5786,7 +5786,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>85.98139190673828</v>
+        <v>85.98139953613281</v>
       </c>
       <c r="C202" t="n">
         <v>92.16999816894531</v>
@@ -5815,7 +5815,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>98.9014892578125</v>
+        <v>98.90147399902344</v>
       </c>
       <c r="C203" t="n">
         <v>106.0199966430664</v>
@@ -5844,7 +5844,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>96.88099670410156</v>
+        <v>96.88100433349609</v>
       </c>
       <c r="C204" t="n">
         <v>103.2399978637695</v>
@@ -5931,7 +5931,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>102.8679428100586</v>
+        <v>102.8679580688477</v>
       </c>
       <c r="C207" t="n">
         <v>109.0800018310547</v>
@@ -5960,7 +5960,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>90.68375396728516</v>
+        <v>90.68373870849609</v>
       </c>
       <c r="C208" t="n">
         <v>96.16000366210938</v>
@@ -5989,7 +5989,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>91.75881958007812</v>
+        <v>91.75882720947266</v>
       </c>
       <c r="C209" t="n">
         <v>97.30000305175781</v>
@@ -6018,7 +6018,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>98.9544677734375</v>
+        <v>98.95446014404297</v>
       </c>
       <c r="C210" t="n">
         <v>104.2099990844727</v>
@@ -6047,7 +6047,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>103.8542251586914</v>
+        <v>103.8542404174805</v>
       </c>
       <c r="C211" t="n">
         <v>109.370002746582</v>
@@ -6076,7 +6076,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>111.1184158325195</v>
+        <v>111.1184234619141</v>
       </c>
       <c r="C212" t="n">
         <v>117.0199966430664</v>
@@ -6105,7 +6105,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>97.74562072753906</v>
+        <v>97.74561309814453</v>
       </c>
       <c r="C213" t="n">
         <v>102.3899993896484</v>
@@ -6221,7 +6221,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>125.8953552246094</v>
+        <v>125.8953247070312</v>
       </c>
       <c r="C217" t="n">
         <v>131.1199951171875</v>
@@ -6250,7 +6250,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>129.9279937744141</v>
+        <v>129.9280090332031</v>
       </c>
       <c r="C218" t="n">
         <v>135.3200073242188</v>
@@ -6308,7 +6308,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>143.5936889648438</v>
+        <v>143.5936737060547</v>
       </c>
       <c r="C220" t="n">
         <v>148.8899993896484</v>
@@ -6337,7 +6337,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>138.327880859375</v>
+        <v>138.3279113769531</v>
       </c>
       <c r="C221" t="n">
         <v>143.4299926757812</v>
@@ -6366,7 +6366,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>133.2955169677734</v>
+        <v>133.2954864501953</v>
       </c>
       <c r="C222" t="n">
         <v>137.6300048828125</v>
@@ -6395,7 +6395,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>134.0897064208984</v>
+        <v>134.0896606445312</v>
       </c>
       <c r="C223" t="n">
         <v>138.4499969482422</v>
@@ -6424,7 +6424,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>146.6318206787109</v>
+        <v>146.6318359375</v>
       </c>
       <c r="C224" t="n">
         <v>151.3999938964844</v>
@@ -6453,7 +6453,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>142.9387817382812</v>
+        <v>142.9387969970703</v>
       </c>
       <c r="C225" t="n">
         <v>146.9299926757812</v>
@@ -6482,7 +6482,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>145.6627044677734</v>
+        <v>145.6627349853516</v>
       </c>
       <c r="C226" t="n">
         <v>149.7299957275391</v>
@@ -6511,7 +6511,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>158.3679504394531</v>
+        <v>158.3679656982422</v>
       </c>
       <c r="C227" t="n">
         <v>162.7899932861328</v>
@@ -6540,7 +6540,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>187.4002838134766</v>
+        <v>187.4002990722656</v>
       </c>
       <c r="C228" t="n">
         <v>192.0099945068359</v>
@@ -6569,7 +6569,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>174.0389709472656</v>
+        <v>174.0389556884766</v>
       </c>
       <c r="C229" t="n">
         <v>178.3200073242188</v>
@@ -6598,7 +6598,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>198.8194122314453</v>
+        <v>198.8193969726562</v>
       </c>
       <c r="C230" t="n">
         <v>203.7100067138672</v>
@@ -6627,7 +6627,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>196.3179168701172</v>
+        <v>196.3179321289062</v>
       </c>
       <c r="C231" t="n">
         <v>200.5500030517578</v>
@@ -6656,7 +6656,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>175.516357421875</v>
+        <v>175.5163421630859</v>
       </c>
       <c r="C232" t="n">
         <v>179.3000030517578</v>
@@ -6685,7 +6685,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>176.4561004638672</v>
+        <v>176.4560852050781</v>
       </c>
       <c r="C233" t="n">
         <v>180.2599945068359</v>
@@ -6743,7 +6743,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>208.9350891113281</v>
+        <v>208.9350738525391</v>
       </c>
       <c r="C235" t="n">
         <v>212.7599945068359</v>
@@ -6772,7 +6772,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>211.1348114013672</v>
+        <v>211.1348266601562</v>
       </c>
       <c r="C236" t="n">
         <v>215</v>
@@ -6859,7 +6859,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>216.6230316162109</v>
+        <v>216.623046875</v>
       </c>
       <c r="C239" t="n">
         <v>219.9900054931641</v>
@@ -6888,7 +6888,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>216.5375213623047</v>
+        <v>216.5375366210938</v>
       </c>
       <c r="C240" t="n">
         <v>219.0700073242188</v>
@@ -6946,7 +6946,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>216.3991241455078</v>
+        <v>216.3991394042969</v>
       </c>
       <c r="C242" t="n">
         <v>218.9299926757812</v>
